--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_340_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_340_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6894</v>
+        <v>5.6981</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9901</v>
+        <v>2.5366</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6992</v>
+        <v>3.1615</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2991</v>
@@ -610,13 +610,13 @@
         <v>4.639</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2899</v>
+        <v>0.2987</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1712</v>
+        <v>-0.6247</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4611</v>
+        <v>0.9234</v>
       </c>
       <c r="V2" t="n">
         <v>3.6109</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8201</v>
+        <v>4.5779</v>
       </c>
       <c r="E3" t="n">
-        <v>4.277</v>
+        <v>4.8667</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4568</v>
+        <v>-0.2888</v>
       </c>
       <c r="G3" t="n">
         <v>2.7487</v>
@@ -688,13 +688,13 @@
         <v>4.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7842</v>
+        <v>-0.0264</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1633</v>
+        <v>-0.5735</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3791</v>
+        <v>0.5472</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6675</v>
+        <v>1.984</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2047</v>
+        <v>-1.1946</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4628</v>
+        <v>3.1787</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5641</v>
+        <v>-3.1455</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7372</v>
+        <v>-2.048</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8269</v>
+        <v>-1.0975</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8548</v>
+        <v>-1.0328</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3359</v>
+        <v>-0.5742</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5189</v>
+        <v>-0.4586</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2907</v>
+        <v>-2.1126</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5987</v>
+        <v>-1.4738</v>
       </c>
       <c r="O4" t="n">
-        <v>0.308</v>
+        <v>-0.6389</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>3.9432</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>4.4071</v>
+        <v>4.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2161</v>
+        <v>-0.7852</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3848</v>
+        <v>-1.0021</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1687</v>
+        <v>0.2168</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6083</v>
+        <v>1.9716</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.8223</v>
+        <v>0.8994</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6022</v>
+        <v>1.7771</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5594</v>
+        <v>1.3982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0428</v>
+        <v>0.3789</v>
       </c>
       <c r="G5" t="n">
         <v>3.9138</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.7451</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1019</v>
+        <v>-0.2631</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.4819</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5801</v>
+        <v>1.4316</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4305</v>
+        <v>0.9688</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0106</v>
+        <v>0.4628</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.1455</v>
+        <v>2.5641</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.048</v>
+        <v>0.7372</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0975</v>
+        <v>1.8269</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0328</v>
+        <v>3.8548</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5742</v>
+        <v>2.3359</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4586</v>
+        <v>1.5189</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1126</v>
+        <v>-1.2907</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4738</v>
+        <v>-1.5987</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6389</v>
+        <v>0.308</v>
       </c>
       <c r="P6" t="n">
-        <v>3.9432</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>4.1751</v>
+        <v>4.4071</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1892</v>
+        <v>-0.452</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.238</v>
+        <v>-0.6207</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0488</v>
+        <v>0.1687</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9716</v>
+        <v>-1.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8994</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1556</v>
+        <v>-0.1065</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2403</v>
+        <v>-0.4015</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3958</v>
+        <v>0.295</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9370000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3967</v>
+        <v>0.1346</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3462</v>
+        <v>0.1849</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0505</v>
+        <v>-0.0503</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3165</v>
+        <v>-0.512</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.4401</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1538</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6761</v>
@@ -1078,13 +1078,13 @@
         <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4138</v>
+        <v>0.2183</v>
       </c>
       <c r="T8" t="n">
-        <v>0.543</v>
+        <v>0.1458</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1291</v>
+        <v>0.0725</v>
       </c>
       <c r="V8" t="n">
         <v>-1.214</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0969</v>
+        <v>-1.1977</v>
       </c>
       <c r="E9" t="n">
         <v>0.4989</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5959</v>
+        <v>-1.6967</v>
       </c>
       <c r="G9" t="n">
         <v>0.2902</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.315</v>
+        <v>-0.4158</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1656</v>
+        <v>-0.2664</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4198</v>
+        <v>-2.5975</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8456</v>
+        <v>-3.8889</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4258</v>
+        <v>1.2914</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0445</v>
@@ -1234,13 +1234,13 @@
         <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.854</v>
+        <v>0.6763</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2794</v>
+        <v>0.2361</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5746</v>
+        <v>0.4402</v>
       </c>
       <c r="V10" t="n">
         <v>0.9304</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.6724</v>
+        <v>8.045699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0499</v>
+        <v>3.423299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>4.622199999999999</v>
+        <v>4.622400000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8242000000000007</v>
@@ -1360,7 +1360,7 @@
         <v>-6.3448</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5206</v>
+        <v>5.520599999999999</v>
       </c>
       <c r="J12" t="n">
         <v>11.849</v>
@@ -1390,13 +1390,13 @@
         <v>25.5147</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2405</v>
+        <v>-1.8671</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.3387</v>
+        <v>-2.9654</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0983</v>
+        <v>1.0984</v>
       </c>
       <c r="V12" t="n">
         <v>2.6184</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2232</v>
+        <v>4.5834</v>
       </c>
       <c r="E13" t="n">
         <v>3.3224</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9008</v>
+        <v>1.261</v>
       </c>
       <c r="G13" t="n">
         <v>4.921</v>
@@ -1468,13 +1468,13 @@
         <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1784</v>
+        <v>0.5386</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4086</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5869</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>0.2836</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6175</v>
+        <v>2.7432</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3988</v>
+        <v>2.1996</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2187</v>
+        <v>0.5436</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2318</v>
+        <v>2.5388</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8704</v>
+        <v>2.1609</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3614</v>
+        <v>0.378</v>
       </c>
       <c r="J14" t="n">
-        <v>1.718</v>
+        <v>4.1042</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0923</v>
+        <v>1.9865</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6257</v>
+        <v>2.1177</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4862</v>
+        <v>-1.5654</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.222</v>
+        <v>0.1744</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2643</v>
+        <v>-1.7398</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2921</v>
+        <v>0.2919</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3734</v>
+        <v>-0.3378</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0813</v>
+        <v>0.6297</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>1.214</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1268</v>
+        <v>1.8084</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4919</v>
+        <v>1.3988</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3651</v>
+        <v>0.4096</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5388</v>
+        <v>1.2318</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1609</v>
+        <v>0.8704</v>
       </c>
       <c r="I15" t="n">
-        <v>0.378</v>
+        <v>0.3614</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1042</v>
+        <v>1.718</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9865</v>
+        <v>1.0923</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1177</v>
+        <v>0.6257</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5654</v>
+        <v>-0.4862</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1744</v>
+        <v>-0.222</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7398</v>
+        <v>-0.2643</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-3.7112</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3245</v>
+        <v>-0.1013</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0455</v>
+        <v>-0.3734</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2789</v>
+        <v>0.2721</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1042</v>
+        <v>1.5444</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5075</v>
+        <v>0.4481</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5967</v>
+        <v>1.0963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0741</v>
+        <v>-1.3435</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1716</v>
+        <v>0.3662</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0975</v>
+        <v>-1.7097</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5528</v>
+        <v>-0.2424</v>
       </c>
       <c r="K16" t="n">
-        <v>0.911</v>
+        <v>1.1462</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3581</v>
+        <v>-1.3887</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4787</v>
+        <v>-1.1011</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2606</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3211</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8909</v>
+        <v>0.4599</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9752</v>
+        <v>-0.3457</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0843</v>
+        <v>0.8057</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7886</v>
+        <v>2.428</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7886</v>
+        <v>2.428</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0625</v>
+        <v>0.9976</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.1536</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3785</v>
+        <v>0.844</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3435</v>
+        <v>0.0741</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3662</v>
+        <v>1.1716</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7097</v>
+        <v>-1.0975</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2424</v>
+        <v>0.5528</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1462</v>
+        <v>0.911</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3887</v>
+        <v>-0.3581</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1011</v>
+        <v>-0.4787</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>0.2606</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3211</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.022</v>
+        <v>0.7844</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1098</v>
+        <v>0.6214</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.163</v>
       </c>
       <c r="V17" t="n">
-        <v>2.428</v>
+        <v>-0.7886</v>
       </c>
       <c r="W17" t="n">
-        <v>2.428</v>
+        <v>-0.7886</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1163</v>
+        <v>-1.6597</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.866</v>
+        <v>-1.2198</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2503</v>
+        <v>-0.4398</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5294</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7199</v>
+        <v>1.1764</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5272</v>
+        <v>0.1733</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1927</v>
+        <v>1.0031</v>
       </c>
       <c r="V18" t="n">
         <v>-2.0026</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2301</v>
+        <v>-1.6998</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0866</v>
+        <v>-1.1115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1435</v>
+        <v>-0.5884</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1065</v>
+        <v>0.6894</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0923</v>
+        <v>1.1009</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0142</v>
+        <v>-0.4115</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9021</v>
+        <v>1.483</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1526</v>
+        <v>1.6805</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.1975</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2044</v>
+        <v>-0.7937</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0602</v>
+        <v>-0.5796</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2647</v>
+        <v>-0.214</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1084</v>
+        <v>0.0747</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9752</v>
+        <v>-0.275</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1331</v>
+        <v>0.3497</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3289</v>
+        <v>-2.3667</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5833</v>
+        <v>-0.9606</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7456</v>
+        <v>-1.406</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6894</v>
+        <v>-2.0546</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1009</v>
+        <v>-1.228</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4115</v>
+        <v>-0.8265</v>
       </c>
       <c r="J20" t="n">
-        <v>1.483</v>
+        <v>0.2975</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6805</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1975</v>
+        <v>0.3879</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7937</v>
+        <v>-2.3521</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5796</v>
+        <v>-1.1377</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.214</v>
+        <v>-1.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-3.7112</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5544</v>
+        <v>-0.0648</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7468</v>
+        <v>-0.3692</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1924</v>
+        <v>0.3044</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5133</v>
+        <v>-2.5847</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.615</v>
+        <v>-2.6764</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8983</v>
+        <v>0.0917</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6469</v>
+        <v>-3.1065</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0384</v>
+        <v>-1.0923</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3915</v>
+        <v>-2.0142</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6754</v>
+        <v>-1.9021</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6421</v>
+        <v>-1.1526</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0333</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0285</v>
+        <v>-1.2044</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3963</v>
+        <v>0.0602</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4248</v>
+        <v>-1.2647</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.912</v>
+        <v>0.7538</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1889</v>
+        <v>0.3855</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7231</v>
+        <v>0.3684</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6176</v>
+        <v>-3.592</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0897</v>
+        <v>-2.8509</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5279</v>
+        <v>-0.7411</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2441</v>
+        <v>0.6469</v>
       </c>
       <c r="H22" t="n">
-        <v>0.449</v>
+        <v>1.0384</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.693</v>
+        <v>-0.3915</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2753</v>
+        <v>0.6754</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9144</v>
+        <v>0.6421</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6391</v>
+        <v>0.0333</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5194</v>
+        <v>-0.0285</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4655</v>
+        <v>0.3963</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0539</v>
+        <v>-0.4248</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3223</v>
+        <v>0.8334</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1142</v>
+        <v>-0.047</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2081</v>
+        <v>0.8804</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6083</v>
+        <v>-3.2166</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0002</v>
+        <v>-4.3012</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7863</v>
+        <v>-3.3256</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2139</v>
+        <v>-0.9755</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0546</v>
+        <v>-1.2441</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.228</v>
+        <v>0.449</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8265</v>
+        <v>-1.693</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2975</v>
+        <v>0.2753</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.9144</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3879</v>
+        <v>-0.6391</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3521</v>
+        <v>-1.5194</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1377</v>
+        <v>-0.4655</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2144</v>
+        <v>-1.0539</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8556</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7112</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6983</v>
+        <v>0.6387</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1949</v>
+        <v>-0.1217</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5034</v>
+        <v>0.7604</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6083</v>
+        <v>-1.6083</v>
       </c>
       <c r="W23" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6722</v>
+        <v>-4.527099999999998</v>
       </c>
       <c r="E24" t="n">
         <v>-4.622300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0499</v>
+        <v>0.09539999999999993</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8239000000000001</v>
+        <v>0.8239000000000005</v>
       </c>
       <c r="H24" t="n">
         <v>6.3448</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.520499999999999</v>
+        <v>-5.5205</v>
       </c>
       <c r="J24" t="n">
         <v>12.6729</v>
@@ -2320,22 +2320,22 @@
         <v>-8.118400000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-25.51479999999999</v>
+        <v>-25.5148</v>
       </c>
       <c r="R24" t="n">
         <v>17.3965</v>
       </c>
       <c r="S24" t="n">
-        <v>2.240600000000001</v>
+        <v>5.3857</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0983</v>
+        <v>-1.0982</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3389</v>
+        <v>6.484</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.618300000000001</v>
+        <v>-2.6183</v>
       </c>
       <c r="W24" t="n">
         <v>9.3177</v>
